--- a/progress/SLR/precision_sample.xlsx
+++ b/progress/SLR/precision_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git2026\research-progress\progress\SLR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36A2759-A26A-4A34-8A3E-C7E7F6B0390B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458A63B4-6889-4BAC-A139-A90D5F977B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="1000" windowWidth="19680" windowHeight="18920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="1690" windowWidth="22880" windowHeight="18920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
